--- a/public/formsExcelTemplates/Evaluación psicológica inicial.xlsx
+++ b/public/formsExcelTemplates/Evaluación psicológica inicial.xlsx
@@ -100,7 +100,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -223,6 +223,21 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -232,58 +247,56 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
@@ -331,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -361,21 +374,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -943,14 +959,14 @@
     </row>
     <row r="4">
       <c r="A4" s="7"/>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="9"/>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="12"/>
@@ -966,14 +982,14 @@
     </row>
     <row r="7">
       <c r="A7" s="7"/>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="9"/>
     </row>
     <row r="8" ht="15">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="8" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="12"/>
@@ -988,18 +1004,18 @@
       <c r="C9" s="6"/>
     </row>
     <row r="10" ht="15">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="12"/>
     </row>
     <row r="11" ht="15">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
